--- a/data/trans_orig/P21D_5_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205297</t>
+          <t>206046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235213</t>
+          <t>235418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441794</t>
+          <t>442228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447308</t>
+          <t>447406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90690</t>
+          <t>90723</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140460</t>
+          <t>140046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144994</t>
+          <t>144970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234217</t>
+          <t>234451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239774</t>
+          <t>239861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,62 +1794,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134729</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380605</t>
+          <t>381468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1857</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69412</t>
+          <t>69494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140209</t>
+          <t>140245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2788,97 +2788,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1338</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4337</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302517</t>
+          <t>302304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>613653</t>
+          <t>614337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>550733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>341841</t>
+          <t>342268</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>347739</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>895274</t>
+          <t>894813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>902082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,98%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1654702</t>
+          <t>1654386</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1662825</t>
+          <t>1662916</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1580255</t>
+          <t>1580377</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1589150</t>
+          <t>1589055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3240081</t>
+          <t>3239555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3251006</t>
+          <t>3250484</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_5_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Provincia-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>595</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>210269</t>
+          <t>220737</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206046</t>
+          <t>217401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>235972</t>
+          <t>250933</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235418</t>
+          <t>247891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>446241</t>
+          <t>471670</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442228</t>
+          <t>466702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>92394</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90723</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>143708</t>
+          <t>144484</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140046</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144970</t>
+          <t>145775</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>237928</t>
+          <t>236878</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234451</t>
+          <t>233076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239861</t>
+          <t>238753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>172729</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135142</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>386253</t>
+          <t>374237</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381468</t>
+          <t>369230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70999</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69494</t>
+          <t>77694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>141703</t>
+          <t>163420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140245</t>
+          <t>161514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305516</t>
+          <t>354784</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>350693</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>617088</t>
+          <t>706436</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614337</t>
+          <t>703331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3161,22 +3161,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>346072</t>
+          <t>404561</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342268</t>
+          <t>399930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>406357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>899987</t>
+          <t>765228</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>894813</t>
+          <t>759622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902082</t>
+          <t>767025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,67 +3469,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3582,69 +3582,69 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1660233</t>
+          <t>1563733</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1654386</t>
+          <t>1558544</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1662916</t>
+          <t>1566129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,94%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1687695</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1681826</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1691005</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2362</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1586096</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1580377</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1589055</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>3817</t>
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3246329</t>
+          <t>3251428</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3239555</t>
+          <t>3244752</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3250484</t>
+          <t>3255790</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
